--- a/final-test-suite-report.xlsx
+++ b/final-test-suite-report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Metric</t>
   </si>
@@ -19,19 +19,25 @@
     <t>Value</t>
   </si>
   <si>
-    <t>Total Selenium Tests</t>
-  </si>
-  <si>
-    <t>Total Load Tests</t>
-  </si>
-  <si>
-    <t>Total Security Tests</t>
+    <t>Total Tests</t>
+  </si>
+  <si>
+    <t>Total Passed</t>
+  </si>
+  <si>
+    <t>Total Failed</t>
+  </si>
+  <si>
+    <t>Overall Pass Rate</t>
+  </si>
+  <si>
+    <t>100.00%</t>
   </si>
   <si>
     <t>Overall Status</t>
   </si>
   <si>
-    <t>FAIL (due to deliberate test failures injected)</t>
+    <t>PASS</t>
   </si>
 </sst>
 </file>
@@ -408,8 +414,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="2" width="30" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -424,7 +433,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>300</v>
+        <v>900</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -432,7 +441,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>300</v>
+        <v>900</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -440,7 +449,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -449,6 +458,14 @@
       </c>
       <c r="B5" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
